--- a/CSC 4500 GitHub/Department.xlsx
+++ b/CSC 4500 GitHub/Department.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\AU\CSC 4500 GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C6FEAA99-3DF8-471E-BE79-1A04B0B17091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DD92195-D84D-40FA-9509-EFFF13489F3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8730" yWindow="1785" windowWidth="21765" windowHeight="13560" xr2:uid="{842AA9E3-26F7-4509-ABDB-6D546FAF5ABD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{842AA9E3-26F7-4509-ABDB-6D546FAF5ABD}"/>
   </bookViews>
   <sheets>
     <sheet name="Department" sheetId="1" r:id="rId1"/>
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <t>Dept ID</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Department</t>
   </si>
@@ -895,42 +892,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{030EA195-F22B-4D0A-B3FA-A3880608188F}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="25.42578125" customWidth="1"/>
+    <col min="1" max="1" width="25.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/CSC 4500 GitHub/Department.xlsx
+++ b/CSC 4500 GitHub/Department.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\AU\CSC 4500 GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DD92195-D84D-40FA-9509-EFFF13489F3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ED3188B-5401-46A7-B3DC-2EA2971D5EAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{842AA9E3-26F7-4509-ABDB-6D546FAF5ABD}"/>
   </bookViews>
@@ -20,7 +20,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+  <si>
+    <t>Dept ID</t>
+  </si>
   <si>
     <t>Department</t>
   </si>
@@ -892,30 +895,42 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{030EA195-F22B-4D0A-B3FA-A3880608188F}">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.42578125" customWidth="1"/>
+    <col min="2" max="2" width="25.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
